--- a/MD80_Main_Input.xlsx
+++ b/MD80_Main_Input.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/williamlampe/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{326E3FF1-50BD-AB47-AA0F-09F4A2267535}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{581E3936-8159-124F-8C72-7B12357FAC67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="1" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="14500" windowHeight="18980" activeTab="2" xr2:uid="{904FC4B5-3CDE-421B-8E98-23A2C72E8C1E}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable Reference" sheetId="15" r:id="rId1"/>
@@ -360,7 +360,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="451" uniqueCount="248">
   <si>
     <t>Length_f</t>
   </si>
@@ -1098,6 +1098,12 @@
   </si>
   <si>
     <t>MD80</t>
+  </si>
+  <si>
+    <t>DSMA-523A</t>
+  </si>
+  <si>
+    <t>NACA 0004</t>
   </si>
 </sst>
 </file>
@@ -5611,6 +5617,166 @@
       <c r="A8" s="10" t="s">
         <v>245</v>
       </c>
+      <c r="B8" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="C8" s="10">
+        <v>0.11</v>
+      </c>
+      <c r="D8" s="10">
+        <v>0.36</v>
+      </c>
+      <c r="E8" s="10">
+        <v>-0.36480000000000001</v>
+      </c>
+      <c r="F8" s="10">
+        <v>-0.22969999999999999</v>
+      </c>
+      <c r="G8" s="10">
+        <v>-9.06E-2</v>
+      </c>
+      <c r="H8" s="10">
+        <v>9.1499999999999998E-2</v>
+      </c>
+      <c r="I8" s="10">
+        <v>0.25209999999999999</v>
+      </c>
+      <c r="J8" s="10">
+        <v>0.3926</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0.4924</v>
+      </c>
+      <c r="L8" s="10">
+        <v>0.59919999999999995</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0.70809999999999995</v>
+      </c>
+      <c r="N8" s="10">
+        <v>0.81489999999999996</v>
+      </c>
+      <c r="O8" s="10">
+        <v>0.92130000000000001</v>
+      </c>
+      <c r="P8" s="10">
+        <v>1.0299</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>1.1337999999999999</v>
+      </c>
+      <c r="R8" s="10">
+        <v>1.2350000000000001</v>
+      </c>
+      <c r="S8" s="10">
+        <v>1.3317000000000001</v>
+      </c>
+      <c r="T8" s="10">
+        <v>1.4271</v>
+      </c>
+      <c r="U8" s="10">
+        <v>1.5059</v>
+      </c>
+      <c r="V8" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="W8" s="10">
+        <v>1.5843</v>
+      </c>
+      <c r="X8" s="10">
+        <v>1.2370000000000001E-2</v>
+      </c>
+      <c r="Y8" s="10">
+        <v>1.1509999999999999E-2</v>
+      </c>
+      <c r="Z8" s="10">
+        <v>1.082E-2</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>9.1400000000000006E-3</v>
+      </c>
+      <c r="AB8" s="10">
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AC8" s="10">
+        <v>8.1300000000000001E-3</v>
+      </c>
+      <c r="AD8" s="10">
+        <v>1.027E-2</v>
+      </c>
+      <c r="AE8" s="10">
+        <v>1.1220000000000001E-2</v>
+      </c>
+      <c r="AF8" s="10">
+        <v>1.2160000000000001E-2</v>
+      </c>
+      <c r="AG8" s="10">
+        <v>1.312E-2</v>
+      </c>
+      <c r="AH8" s="10">
+        <v>1.4200000000000001E-2</v>
+      </c>
+      <c r="AI8" s="10">
+        <v>1.5100000000000001E-2</v>
+      </c>
+      <c r="AJ8" s="10">
+        <v>1.651E-2</v>
+      </c>
+      <c r="AK8" s="10">
+        <v>1.806E-2</v>
+      </c>
+      <c r="AL8" s="10">
+        <v>1.9970000000000002E-2</v>
+      </c>
+      <c r="AM8" s="10">
+        <v>2.1649999999999999E-2</v>
+      </c>
+      <c r="AN8" s="10">
+        <v>2.487E-2</v>
+      </c>
+      <c r="AO8" s="10">
+        <v>2.726E-2</v>
+      </c>
+      <c r="AP8" s="10">
+        <f>MIN(X8:AO8)</f>
+        <v>6.3699999999999998E-3</v>
+      </c>
+      <c r="AQ8" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="AR8" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AS8" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AT8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="10">
+        <v>0</v>
+      </c>
+      <c r="AW8" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="AX8" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="AY8" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="AZ8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BA8" s="10">
+        <v>0</v>
+      </c>
+      <c r="BB8" s="10">
+        <v>0</v>
+      </c>
     </row>
     <row r="21" s="23" customFormat="1" x14ac:dyDescent="0.2"/>
   </sheetData>
